--- a/medical_application_forms/045_dermal_filler_aftercare_form--medical_application_forms.xlsx
+++ b/medical_application_forms/045_dermal_filler_aftercare_form--medical_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="49" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'face',_'value':_'face'}</t>
+          <t>face</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Face', 'value': 'face'}</t>
+          <t>Face</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'lips',_'value':_'lips'}</t>
+          <t>lips</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Lips', 'value': 'lips'}</t>
+          <t>Lips</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'hands',_'value':_'hands'}</t>
+          <t>hands</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Hands', 'value': 'hands'}</t>
+          <t>Hands</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'feet',_'value':_'feet'}</t>
+          <t>feet</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Feet', 'value': 'feet'}</t>
+          <t>Feet</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'moisturizer',_'value':_'moisturizer'}</t>
+          <t>moisturizer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Moisturizer', 'value': 'moisturizer'}</t>
+          <t>Moisturizer</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'sunscreen',_'value':_'sunscreen'}</t>
+          <t>sunscreen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Sunscreen', 'value': 'sunscreen'}</t>
+          <t>Sunscreen</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'antioxidant',_'value':_'antioxidant'}</t>
+          <t>antioxidant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Antioxidant', 'value': 'antioxidant'}</t>
+          <t>Antioxidant</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'redness',_'value':_'redness'}</t>
+          <t>redness</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Redness', 'value': 'redness'}</t>
+          <t>Redness</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'swelling',_'value':_'swelling'}</t>
+          <t>swelling</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Swelling', 'value': 'swelling'}</t>
+          <t>Swelling</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'blisters',_'value':_'blisters'}</t>
+          <t>blisters</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Blisters', 'value': 'blisters'}</t>
+          <t>Blisters</t>
         </is>
       </c>
     </row>
@@ -956,131 +956,63 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'pain',_'value':_'pain'}</t>
+          <t>pain</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Pain', 'value': 'pain'}</t>
+          <t>Pain</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dermal_filler_aftercare_adverse_effects_choices</t>
+          <t>dermal_filler_aftercare_follow_up_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'redness',_'value':_'redness'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Redness', 'value': 'redness'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dermal_filler_aftercare_adverse_effects_choices</t>
+          <t>dermal_filler_aftercare_follow_up_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'swelling',_'value':_'swelling'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Swelling', 'value': 'swelling'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dermal_filler_aftercare_adverse_effects_choices</t>
+          <t>dermal_filler_aftercare_follow_up_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'blisters',_'value':_'blisters'}</t>
+          <t>in_office</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Blisters', 'value': 'blisters'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>dermal_filler_aftercare_adverse_effects_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'label':_'pain',_'value':_'pain'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'label': 'Pain', 'value': 'pain'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>dermal_filler_aftercare_follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'label':_'phone',_'value':_'phone'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'label': 'Phone', 'value': 'phone'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>dermal_filler_aftercare_follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'label':_'email',_'value':_'email'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'label': 'Email', 'value': 'email'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>dermal_filler_aftercare_follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'label':_'in_office',_'value':_'in_office'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'label': 'In Office', 'value': 'in_office'}</t>
+          <t>In Office</t>
         </is>
       </c>
     </row>
